--- a/Nuevos DeepWins/Problem2_Checkerboard6x6/Res/Comparativa_9_Neuronas.xlsx
+++ b/Nuevos DeepWins/Problem2_Checkerboard6x6/Res/Comparativa_9_Neuronas.xlsx
@@ -581,7 +581,7 @@
         <v>0.1</v>
       </c>
       <c r="B2" t="n">
-        <v>0.248853</v>
+        <v>0.249137</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -598,25 +598,25 @@
         <v>200000</v>
       </c>
       <c r="G2" t="n">
-        <v>0.521739</v>
+        <v>0.525358</v>
       </c>
       <c r="H2" t="n">
-        <v>0.514502</v>
+        <v>0.509458</v>
       </c>
       <c r="I2" t="n">
-        <v>0.518095</v>
+        <v>0.517286</v>
       </c>
       <c r="J2" t="n">
-        <v>0.252321</v>
+        <v>0.251934</v>
       </c>
       <c r="K2" t="n">
-        <v>0.427861</v>
+        <v>0.437811</v>
       </c>
       <c r="L2" t="n">
-        <v>0.459893</v>
+        <v>0.470588</v>
       </c>
       <c r="M2" t="n">
-        <v>0.443299</v>
+        <v>0.453608</v>
       </c>
       <c r="N2" t="n">
         <v>0.2</v>
@@ -652,7 +652,7 @@
       </c>
       <c r="X2" t="inlineStr">
         <is>
-          <t>_2_3_3_3_1_1790730015_4.txt</t>
+          <t>_2_3_3_3_1_1790730015_9.txt</t>
         </is>
       </c>
       <c r="Y2" t="inlineStr">
@@ -682,42 +682,42 @@
         <v>0.1</v>
       </c>
       <c r="B3" t="n">
-        <v>0.249359</v>
+        <v>0.21524</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>_2_3_3_3_1_</t>
+          <t>_2_9_1_</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>1790730015</v>
+        <v>1790729965</v>
       </c>
       <c r="E3" t="n">
-        <v>127</v>
+        <v>50</v>
       </c>
       <c r="F3" t="n">
         <v>200000</v>
       </c>
       <c r="G3" t="n">
-        <v>0.5199009999999999</v>
+        <v>0.617478</v>
       </c>
       <c r="H3" t="n">
-        <v>0.527112</v>
+        <v>0.543506</v>
       </c>
       <c r="I3" t="n">
-        <v>0.523481</v>
+        <v>0.578135</v>
       </c>
       <c r="J3" t="n">
-        <v>0.251712</v>
+        <v>0.215919</v>
       </c>
       <c r="K3" t="n">
-        <v>0.425121</v>
+        <v>0.6</v>
       </c>
       <c r="L3" t="n">
-        <v>0.470588</v>
+        <v>0.513369</v>
       </c>
       <c r="M3" t="n">
-        <v>0.4467</v>
+        <v>0.553314</v>
       </c>
       <c r="N3" t="n">
         <v>0.2</v>
@@ -753,23 +753,23 @@
       </c>
       <c r="X3" t="inlineStr">
         <is>
-          <t>_2_3_3_3_1_1790730015_5.txt</t>
+          <t>_2_9_1_1790729965_3.txt</t>
         </is>
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>[3, 3, 3]</t>
+          <t>[9]</t>
         </is>
       </c>
       <c r="Z3" t="n">
         <v>9</v>
       </c>
       <c r="AA3" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>Profunda</t>
+          <t>Angosta</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr">
@@ -783,42 +783,42 @@
         <v>0.1</v>
       </c>
       <c r="B4" t="n">
-        <v>0.220848</v>
+        <v>0.248853</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>_2_9_1_</t>
+          <t>_2_3_3_3_1_</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>1790729965</v>
+        <v>1790730015</v>
       </c>
       <c r="E4" t="n">
-        <v>50</v>
+        <v>127</v>
       </c>
       <c r="F4" t="n">
         <v>200000</v>
       </c>
       <c r="G4" t="n">
-        <v>0.582147</v>
+        <v>0.521739</v>
       </c>
       <c r="H4" t="n">
-        <v>0.567465</v>
+        <v>0.514502</v>
       </c>
       <c r="I4" t="n">
-        <v>0.574713</v>
+        <v>0.518095</v>
       </c>
       <c r="J4" t="n">
-        <v>0.220998</v>
+        <v>0.252321</v>
       </c>
       <c r="K4" t="n">
-        <v>0.576271</v>
+        <v>0.427861</v>
       </c>
       <c r="L4" t="n">
-        <v>0.545455</v>
+        <v>0.459893</v>
       </c>
       <c r="M4" t="n">
-        <v>0.56044</v>
+        <v>0.443299</v>
       </c>
       <c r="N4" t="n">
         <v>0.2</v>
@@ -854,23 +854,23 @@
       </c>
       <c r="X4" t="inlineStr">
         <is>
-          <t>_2_9_1_1790729965_16.txt</t>
+          <t>_2_3_3_3_1_1790730015_4.txt</t>
         </is>
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>[9]</t>
+          <t>[3, 3, 3]</t>
         </is>
       </c>
       <c r="Z4" t="n">
         <v>9</v>
       </c>
       <c r="AA4" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>Angosta</t>
+          <t>Profunda</t>
         </is>
       </c>
       <c r="AC4" t="inlineStr">
@@ -884,42 +884,42 @@
         <v>0.1</v>
       </c>
       <c r="B5" t="n">
-        <v>0.220445</v>
+        <v>0.248857</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>_2_9_1_</t>
+          <t>_2_3_3_3_1_</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>1790729965</v>
+        <v>1790730015</v>
       </c>
       <c r="E5" t="n">
-        <v>50</v>
+        <v>127</v>
       </c>
       <c r="F5" t="n">
         <v>200000</v>
       </c>
       <c r="G5" t="n">
-        <v>0.640703</v>
+        <v>0.508259</v>
       </c>
       <c r="H5" t="n">
-        <v>0.643127</v>
+        <v>0.504414</v>
       </c>
       <c r="I5" t="n">
-        <v>0.641913</v>
+        <v>0.506329</v>
       </c>
       <c r="J5" t="n">
-        <v>0.225795</v>
+        <v>0.252</v>
       </c>
       <c r="K5" t="n">
-        <v>0.593909</v>
+        <v>0.419512</v>
       </c>
       <c r="L5" t="n">
-        <v>0.625668</v>
+        <v>0.459893</v>
       </c>
       <c r="M5" t="n">
-        <v>0.609375</v>
+        <v>0.438776</v>
       </c>
       <c r="N5" t="n">
         <v>0.2</v>
@@ -955,23 +955,23 @@
       </c>
       <c r="X5" t="inlineStr">
         <is>
-          <t>_2_9_1_1790729965_5.txt</t>
+          <t>_2_3_3_3_1_1790730015_8.txt</t>
         </is>
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>[9]</t>
+          <t>[3, 3, 3]</t>
         </is>
       </c>
       <c r="Z5" t="n">
         <v>9</v>
       </c>
       <c r="AA5" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>Angosta</t>
+          <t>Profunda</t>
         </is>
       </c>
       <c r="AC5" t="inlineStr">
@@ -985,42 +985,42 @@
         <v>0.1</v>
       </c>
       <c r="B6" t="n">
-        <v>0.249058</v>
+        <v>0.241282</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>_2_3_3_3_1_</t>
+          <t>_2_9_1_</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>1790730015</v>
+        <v>1790729965</v>
       </c>
       <c r="E6" t="n">
-        <v>127</v>
+        <v>50</v>
       </c>
       <c r="F6" t="n">
         <v>200000</v>
       </c>
       <c r="G6" t="n">
-        <v>0.5179</v>
+        <v>0.577778</v>
       </c>
       <c r="H6" t="n">
-        <v>0.547289</v>
+        <v>0.491803</v>
       </c>
       <c r="I6" t="n">
-        <v>0.532189</v>
+        <v>0.531335</v>
       </c>
       <c r="J6" t="n">
-        <v>0.251632</v>
+        <v>0.241958</v>
       </c>
       <c r="K6" t="n">
-        <v>0.427273</v>
+        <v>0.55625</v>
       </c>
       <c r="L6" t="n">
-        <v>0.502674</v>
+        <v>0.475936</v>
       </c>
       <c r="M6" t="n">
-        <v>0.461916</v>
+        <v>0.512968</v>
       </c>
       <c r="N6" t="n">
         <v>0.2</v>
@@ -1056,23 +1056,23 @@
       </c>
       <c r="X6" t="inlineStr">
         <is>
-          <t>_2_3_3_3_1_1790730015_16.txt</t>
+          <t>_2_9_1_1790729965_14.txt</t>
         </is>
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>[3, 3, 3]</t>
+          <t>[9]</t>
         </is>
       </c>
       <c r="Z6" t="n">
         <v>9</v>
       </c>
       <c r="AA6" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>Profunda</t>
+          <t>Angosta</t>
         </is>
       </c>
       <c r="AC6" t="inlineStr">
@@ -1086,42 +1086,42 @@
         <v>0.1</v>
       </c>
       <c r="B7" t="n">
-        <v>0.222741</v>
+        <v>0.24934</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>_2_9_1_</t>
+          <t>_2_3_3_3_1_</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>1790729965</v>
+        <v>1790730015</v>
       </c>
       <c r="E7" t="n">
-        <v>50</v>
+        <v>127</v>
       </c>
       <c r="F7" t="n">
         <v>200000</v>
       </c>
       <c r="G7" t="n">
-        <v>0.585806</v>
+        <v>0.5199009999999999</v>
       </c>
       <c r="H7" t="n">
-        <v>0.572509</v>
+        <v>0.527112</v>
       </c>
       <c r="I7" t="n">
-        <v>0.579082</v>
+        <v>0.523481</v>
       </c>
       <c r="J7" t="n">
-        <v>0.224211</v>
+        <v>0.251775</v>
       </c>
       <c r="K7" t="n">
-        <v>0.566845</v>
+        <v>0.427184</v>
       </c>
       <c r="L7" t="n">
-        <v>0.566845</v>
+        <v>0.470588</v>
       </c>
       <c r="M7" t="n">
-        <v>0.566845</v>
+        <v>0.447837</v>
       </c>
       <c r="N7" t="n">
         <v>0.2</v>
@@ -1157,23 +1157,23 @@
       </c>
       <c r="X7" t="inlineStr">
         <is>
-          <t>_2_9_1_1790729965_19.txt</t>
+          <t>_2_3_3_3_1_1790730015_11.txt</t>
         </is>
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>[9]</t>
+          <t>[3, 3, 3]</t>
         </is>
       </c>
       <c r="Z7" t="n">
         <v>9</v>
       </c>
       <c r="AA7" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>Angosta</t>
+          <t>Profunda</t>
         </is>
       </c>
       <c r="AC7" t="inlineStr">
@@ -1187,42 +1187,42 @@
         <v>0.1</v>
       </c>
       <c r="B8" t="n">
-        <v>0.24935</v>
+        <v>0.222741</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>_2_3_3_3_1_</t>
+          <t>_2_9_1_</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>1790730015</v>
+        <v>1790729965</v>
       </c>
       <c r="E8" t="n">
-        <v>127</v>
+        <v>50</v>
       </c>
       <c r="F8" t="n">
         <v>200000</v>
       </c>
       <c r="G8" t="n">
-        <v>0.5199009999999999</v>
+        <v>0.585806</v>
       </c>
       <c r="H8" t="n">
-        <v>0.527112</v>
+        <v>0.572509</v>
       </c>
       <c r="I8" t="n">
-        <v>0.523481</v>
+        <v>0.579082</v>
       </c>
       <c r="J8" t="n">
-        <v>0.251762</v>
+        <v>0.224211</v>
       </c>
       <c r="K8" t="n">
-        <v>0.427184</v>
+        <v>0.566845</v>
       </c>
       <c r="L8" t="n">
-        <v>0.470588</v>
+        <v>0.566845</v>
       </c>
       <c r="M8" t="n">
-        <v>0.447837</v>
+        <v>0.566845</v>
       </c>
       <c r="N8" t="n">
         <v>0.2</v>
@@ -1258,23 +1258,23 @@
       </c>
       <c r="X8" t="inlineStr">
         <is>
-          <t>_2_3_3_3_1_1790730015_15.txt</t>
+          <t>_2_9_1_1790729965_19.txt</t>
         </is>
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>[3, 3, 3]</t>
+          <t>[9]</t>
         </is>
       </c>
       <c r="Z8" t="n">
         <v>9</v>
       </c>
       <c r="AA8" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>Profunda</t>
+          <t>Angosta</t>
         </is>
       </c>
       <c r="AC8" t="inlineStr">
@@ -1288,42 +1288,42 @@
         <v>0.1</v>
       </c>
       <c r="B9" t="n">
-        <v>0.249287</v>
+        <v>0.211687</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>_2_3_3_3_1_</t>
+          <t>_2_9_1_</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>1790730015</v>
+        <v>1790729965</v>
       </c>
       <c r="E9" t="n">
-        <v>127</v>
+        <v>50</v>
       </c>
       <c r="F9" t="n">
         <v>200000</v>
       </c>
       <c r="G9" t="n">
-        <v>0.531088</v>
+        <v>0.6815639999999999</v>
       </c>
       <c r="H9" t="n">
-        <v>0.517024</v>
+        <v>0.615385</v>
       </c>
       <c r="I9" t="n">
-        <v>0.523962</v>
+        <v>0.646786</v>
       </c>
       <c r="J9" t="n">
-        <v>0.251839</v>
+        <v>0.210628</v>
       </c>
       <c r="K9" t="n">
-        <v>0.434343</v>
+        <v>0.655367</v>
       </c>
       <c r="L9" t="n">
-        <v>0.459893</v>
+        <v>0.620321</v>
       </c>
       <c r="M9" t="n">
-        <v>0.446753</v>
+        <v>0.637363</v>
       </c>
       <c r="N9" t="n">
         <v>0.2</v>
@@ -1359,23 +1359,23 @@
       </c>
       <c r="X9" t="inlineStr">
         <is>
-          <t>_2_3_3_3_1_1790730015_7.txt</t>
+          <t>_2_9_1_1790729965_7.txt</t>
         </is>
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>[3, 3, 3]</t>
+          <t>[9]</t>
         </is>
       </c>
       <c r="Z9" t="n">
         <v>9</v>
       </c>
       <c r="AA9" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>Profunda</t>
+          <t>Angosta</t>
         </is>
       </c>
       <c r="AC9" t="inlineStr">
@@ -1389,42 +1389,42 @@
         <v>0.1</v>
       </c>
       <c r="B10" t="n">
-        <v>0.21524</v>
+        <v>0.249287</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>_2_9_1_</t>
+          <t>_2_3_3_3_1_</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>1790729965</v>
+        <v>1790730015</v>
       </c>
       <c r="E10" t="n">
-        <v>50</v>
+        <v>127</v>
       </c>
       <c r="F10" t="n">
         <v>200000</v>
       </c>
       <c r="G10" t="n">
-        <v>0.617478</v>
+        <v>0.531088</v>
       </c>
       <c r="H10" t="n">
-        <v>0.543506</v>
+        <v>0.517024</v>
       </c>
       <c r="I10" t="n">
-        <v>0.578135</v>
+        <v>0.523962</v>
       </c>
       <c r="J10" t="n">
-        <v>0.215919</v>
+        <v>0.251839</v>
       </c>
       <c r="K10" t="n">
-        <v>0.6</v>
+        <v>0.434343</v>
       </c>
       <c r="L10" t="n">
-        <v>0.513369</v>
+        <v>0.459893</v>
       </c>
       <c r="M10" t="n">
-        <v>0.553314</v>
+        <v>0.446753</v>
       </c>
       <c r="N10" t="n">
         <v>0.2</v>
@@ -1460,23 +1460,23 @@
       </c>
       <c r="X10" t="inlineStr">
         <is>
-          <t>_2_9_1_1790729965_3.txt</t>
+          <t>_2_3_3_3_1_1790730015_7.txt</t>
         </is>
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>[9]</t>
+          <t>[3, 3, 3]</t>
         </is>
       </c>
       <c r="Z10" t="n">
         <v>9</v>
       </c>
       <c r="AA10" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>Angosta</t>
+          <t>Profunda</t>
         </is>
       </c>
       <c r="AC10" t="inlineStr">
@@ -1490,42 +1490,42 @@
         <v>0.1</v>
       </c>
       <c r="B11" t="n">
-        <v>0.214252</v>
+        <v>0.249454</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>_2_9_1_</t>
+          <t>_2_3_3_3_1_</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>1790729965</v>
+        <v>1790730015</v>
       </c>
       <c r="E11" t="n">
-        <v>50</v>
+        <v>127</v>
       </c>
       <c r="F11" t="n">
         <v>200000</v>
       </c>
       <c r="G11" t="n">
-        <v>0.658537</v>
+        <v>0.523481</v>
       </c>
       <c r="H11" t="n">
-        <v>0.612863</v>
+        <v>0.477932</v>
       </c>
       <c r="I11" t="n">
-        <v>0.634879</v>
+        <v>0.49967</v>
       </c>
       <c r="J11" t="n">
-        <v>0.214906</v>
+        <v>0.251518</v>
       </c>
       <c r="K11" t="n">
-        <v>0.64</v>
+        <v>0.444444</v>
       </c>
       <c r="L11" t="n">
-        <v>0.59893</v>
+        <v>0.449198</v>
       </c>
       <c r="M11" t="n">
-        <v>0.618785</v>
+        <v>0.446809</v>
       </c>
       <c r="N11" t="n">
         <v>0.2</v>
@@ -1561,23 +1561,23 @@
       </c>
       <c r="X11" t="inlineStr">
         <is>
-          <t>_2_9_1_1790729965_8.txt</t>
+          <t>_2_3_3_3_1_1790730015_19.txt</t>
         </is>
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>[9]</t>
+          <t>[3, 3, 3]</t>
         </is>
       </c>
       <c r="Z11" t="n">
         <v>9</v>
       </c>
       <c r="AA11" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>Angosta</t>
+          <t>Profunda</t>
         </is>
       </c>
       <c r="AC11" t="inlineStr">
@@ -1591,42 +1591,42 @@
         <v>0.1</v>
       </c>
       <c r="B12" t="n">
-        <v>0.215543</v>
+        <v>0.249165</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>_2_9_1_</t>
+          <t>_2_3_3_3_1_</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>1790729965</v>
+        <v>1790730015</v>
       </c>
       <c r="E12" t="n">
-        <v>50</v>
+        <v>127</v>
       </c>
       <c r="F12" t="n">
         <v>200000</v>
       </c>
       <c r="G12" t="n">
-        <v>0.673177</v>
+        <v>0.524528</v>
       </c>
       <c r="H12" t="n">
-        <v>0.651955</v>
+        <v>0.525851</v>
       </c>
       <c r="I12" t="n">
-        <v>0.662396</v>
+        <v>0.525189</v>
       </c>
       <c r="J12" t="n">
-        <v>0.228765</v>
+        <v>0.251801</v>
       </c>
       <c r="K12" t="n">
-        <v>0.601064</v>
+        <v>0.42233</v>
       </c>
       <c r="L12" t="n">
-        <v>0.604278</v>
+        <v>0.465241</v>
       </c>
       <c r="M12" t="n">
-        <v>0.602667</v>
+        <v>0.442748</v>
       </c>
       <c r="N12" t="n">
         <v>0.2</v>
@@ -1662,23 +1662,23 @@
       </c>
       <c r="X12" t="inlineStr">
         <is>
-          <t>_2_9_1_1790729965_4.txt</t>
+          <t>_2_3_3_3_1_1790730015_3.txt</t>
         </is>
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>[9]</t>
+          <t>[3, 3, 3]</t>
         </is>
       </c>
       <c r="Z12" t="n">
         <v>9</v>
       </c>
       <c r="AA12" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>Angosta</t>
+          <t>Profunda</t>
         </is>
       </c>
       <c r="AC12" t="inlineStr">
@@ -1692,7 +1692,7 @@
         <v>0.1</v>
       </c>
       <c r="B13" t="n">
-        <v>0.249346</v>
+        <v>0.249058</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1709,25 +1709,25 @@
         <v>200000</v>
       </c>
       <c r="G13" t="n">
-        <v>0.528351</v>
+        <v>0.5179</v>
       </c>
       <c r="H13" t="n">
-        <v>0.517024</v>
+        <v>0.547289</v>
       </c>
       <c r="I13" t="n">
-        <v>0.522626</v>
+        <v>0.532189</v>
       </c>
       <c r="J13" t="n">
-        <v>0.25162</v>
+        <v>0.251632</v>
       </c>
       <c r="K13" t="n">
-        <v>0.435644</v>
+        <v>0.427273</v>
       </c>
       <c r="L13" t="n">
-        <v>0.470588</v>
+        <v>0.502674</v>
       </c>
       <c r="M13" t="n">
-        <v>0.452442</v>
+        <v>0.461916</v>
       </c>
       <c r="N13" t="n">
         <v>0.2</v>
@@ -1763,7 +1763,7 @@
       </c>
       <c r="X13" t="inlineStr">
         <is>
-          <t>_2_3_3_3_1_1790730015_13.txt</t>
+          <t>_2_3_3_3_1_1790730015_16.txt</t>
         </is>
       </c>
       <c r="Y13" t="inlineStr">
@@ -1793,7 +1793,7 @@
         <v>0.1</v>
       </c>
       <c r="B14" t="n">
-        <v>0.249288</v>
+        <v>0.249538</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1810,25 +1810,25 @@
         <v>200000</v>
       </c>
       <c r="G14" t="n">
-        <v>0.526992</v>
+        <v>0.527007</v>
       </c>
       <c r="H14" t="n">
-        <v>0.517024</v>
+        <v>0.455233</v>
       </c>
       <c r="I14" t="n">
-        <v>0.521961</v>
+        <v>0.488498</v>
       </c>
       <c r="J14" t="n">
-        <v>0.251935</v>
+        <v>0.25062</v>
       </c>
       <c r="K14" t="n">
-        <v>0.432161</v>
+        <v>0.44382</v>
       </c>
       <c r="L14" t="n">
-        <v>0.459893</v>
+        <v>0.42246</v>
       </c>
       <c r="M14" t="n">
-        <v>0.445596</v>
+        <v>0.432877</v>
       </c>
       <c r="N14" t="n">
         <v>0.2</v>
@@ -1864,7 +1864,7 @@
       </c>
       <c r="X14" t="inlineStr">
         <is>
-          <t>_2_3_3_3_1_1790730015_14.txt</t>
+          <t>_2_3_3_3_1_1790730015_18.txt</t>
         </is>
       </c>
       <c r="Y14" t="inlineStr">
@@ -1894,7 +1894,7 @@
         <v>0.1</v>
       </c>
       <c r="B15" t="n">
-        <v>0.214497</v>
+        <v>0.214575</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -1911,25 +1911,25 @@
         <v>200000</v>
       </c>
       <c r="G15" t="n">
-        <v>0.635171</v>
+        <v>0.663043</v>
       </c>
       <c r="H15" t="n">
-        <v>0.61034</v>
+        <v>0.615385</v>
       </c>
       <c r="I15" t="n">
-        <v>0.622508</v>
+        <v>0.6383259999999999</v>
       </c>
       <c r="J15" t="n">
-        <v>0.215759</v>
+        <v>0.216217</v>
       </c>
       <c r="K15" t="n">
-        <v>0.606557</v>
+        <v>0.6292140000000001</v>
       </c>
       <c r="L15" t="n">
-        <v>0.593583</v>
+        <v>0.59893</v>
       </c>
       <c r="M15" t="n">
-        <v>0.6</v>
+        <v>0.613699</v>
       </c>
       <c r="N15" t="n">
         <v>0.2</v>
@@ -1965,7 +1965,7 @@
       </c>
       <c r="X15" t="inlineStr">
         <is>
-          <t>_2_9_1_1790729965_15.txt</t>
+          <t>_2_9_1_1790729965_11.txt</t>
         </is>
       </c>
       <c r="Y15" t="inlineStr">
@@ -1995,7 +1995,7 @@
         <v>0.1</v>
       </c>
       <c r="B16" t="n">
-        <v>0.215814</v>
+        <v>0.220445</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2012,25 +2012,25 @@
         <v>200000</v>
       </c>
       <c r="G16" t="n">
-        <v>0.635838</v>
+        <v>0.640703</v>
       </c>
       <c r="H16" t="n">
-        <v>0.554855</v>
+        <v>0.643127</v>
       </c>
       <c r="I16" t="n">
-        <v>0.592593</v>
+        <v>0.641913</v>
       </c>
       <c r="J16" t="n">
-        <v>0.216246</v>
+        <v>0.225795</v>
       </c>
       <c r="K16" t="n">
-        <v>0.63354</v>
+        <v>0.593909</v>
       </c>
       <c r="L16" t="n">
-        <v>0.545455</v>
+        <v>0.625668</v>
       </c>
       <c r="M16" t="n">
-        <v>0.586207</v>
+        <v>0.609375</v>
       </c>
       <c r="N16" t="n">
         <v>0.2</v>
@@ -2066,7 +2066,7 @@
       </c>
       <c r="X16" t="inlineStr">
         <is>
-          <t>_2_9_1_1790729965_1.txt</t>
+          <t>_2_9_1_1790729965_5.txt</t>
         </is>
       </c>
       <c r="Y16" t="inlineStr">
@@ -2096,42 +2096,42 @@
         <v>0.1</v>
       </c>
       <c r="B17" t="n">
-        <v>0.194465</v>
+        <v>0.249291</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>_2_9_1_</t>
+          <t>_2_3_3_3_1_</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>1790729965</v>
+        <v>1790730015</v>
       </c>
       <c r="E17" t="n">
-        <v>50</v>
+        <v>127</v>
       </c>
       <c r="F17" t="n">
         <v>200000</v>
       </c>
       <c r="G17" t="n">
-        <v>0.730159</v>
+        <v>0.5220129999999999</v>
       </c>
       <c r="H17" t="n">
-        <v>0.580076</v>
+        <v>0.523329</v>
       </c>
       <c r="I17" t="n">
-        <v>0.646521</v>
+        <v>0.52267</v>
       </c>
       <c r="J17" t="n">
-        <v>0.207262</v>
+        <v>0.251789</v>
       </c>
       <c r="K17" t="n">
-        <v>0.682759</v>
+        <v>0.426471</v>
       </c>
       <c r="L17" t="n">
-        <v>0.529412</v>
+        <v>0.465241</v>
       </c>
       <c r="M17" t="n">
-        <v>0.596386</v>
+        <v>0.445013</v>
       </c>
       <c r="N17" t="n">
         <v>0.2</v>
@@ -2167,23 +2167,23 @@
       </c>
       <c r="X17" t="inlineStr">
         <is>
-          <t>_2_9_1_1790729965_17.txt</t>
+          <t>_2_3_3_3_1_1790730015_1.txt</t>
         </is>
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>[9]</t>
+          <t>[3, 3, 3]</t>
         </is>
       </c>
       <c r="Z17" t="n">
         <v>9</v>
       </c>
       <c r="AA17" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>Angosta</t>
+          <t>Profunda</t>
         </is>
       </c>
       <c r="AC17" t="inlineStr">
@@ -2197,42 +2197,42 @@
         <v>0.1</v>
       </c>
       <c r="B18" t="n">
-        <v>0.214417</v>
+        <v>0.249346</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>_2_9_1_</t>
+          <t>_2_3_3_3_1_</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>1790729965</v>
+        <v>1790730015</v>
       </c>
       <c r="E18" t="n">
-        <v>50</v>
+        <v>127</v>
       </c>
       <c r="F18" t="n">
         <v>200000</v>
       </c>
       <c r="G18" t="n">
-        <v>0.654619</v>
+        <v>0.528351</v>
       </c>
       <c r="H18" t="n">
-        <v>0.616646</v>
+        <v>0.517024</v>
       </c>
       <c r="I18" t="n">
-        <v>0.635065</v>
+        <v>0.522626</v>
       </c>
       <c r="J18" t="n">
-        <v>0.216019</v>
+        <v>0.25162</v>
       </c>
       <c r="K18" t="n">
-        <v>0.6277779999999999</v>
+        <v>0.435644</v>
       </c>
       <c r="L18" t="n">
-        <v>0.604278</v>
+        <v>0.470588</v>
       </c>
       <c r="M18" t="n">
-        <v>0.615804</v>
+        <v>0.452442</v>
       </c>
       <c r="N18" t="n">
         <v>0.2</v>
@@ -2268,23 +2268,23 @@
       </c>
       <c r="X18" t="inlineStr">
         <is>
-          <t>_2_9_1_1790729965_2.txt</t>
+          <t>_2_3_3_3_1_1790730015_13.txt</t>
         </is>
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>[9]</t>
+          <t>[3, 3, 3]</t>
         </is>
       </c>
       <c r="Z18" t="n">
         <v>9</v>
       </c>
       <c r="AA18" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>Angosta</t>
+          <t>Profunda</t>
         </is>
       </c>
       <c r="AC18" t="inlineStr">
@@ -2298,42 +2298,42 @@
         <v>0.1</v>
       </c>
       <c r="B19" t="n">
-        <v>0.214575</v>
+        <v>0.249288</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>_2_9_1_</t>
+          <t>_2_3_3_3_1_</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>1790729965</v>
+        <v>1790730015</v>
       </c>
       <c r="E19" t="n">
-        <v>50</v>
+        <v>127</v>
       </c>
       <c r="F19" t="n">
         <v>200000</v>
       </c>
       <c r="G19" t="n">
-        <v>0.663043</v>
+        <v>0.526992</v>
       </c>
       <c r="H19" t="n">
-        <v>0.615385</v>
+        <v>0.517024</v>
       </c>
       <c r="I19" t="n">
-        <v>0.6383259999999999</v>
+        <v>0.521961</v>
       </c>
       <c r="J19" t="n">
-        <v>0.216217</v>
+        <v>0.251935</v>
       </c>
       <c r="K19" t="n">
-        <v>0.6292140000000001</v>
+        <v>0.432161</v>
       </c>
       <c r="L19" t="n">
-        <v>0.59893</v>
+        <v>0.459893</v>
       </c>
       <c r="M19" t="n">
-        <v>0.613699</v>
+        <v>0.445596</v>
       </c>
       <c r="N19" t="n">
         <v>0.2</v>
@@ -2369,23 +2369,23 @@
       </c>
       <c r="X19" t="inlineStr">
         <is>
-          <t>_2_9_1_1790729965_11.txt</t>
+          <t>_2_3_3_3_1_1790730015_14.txt</t>
         </is>
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>[9]</t>
+          <t>[3, 3, 3]</t>
         </is>
       </c>
       <c r="Z19" t="n">
         <v>9</v>
       </c>
       <c r="AA19" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>Angosta</t>
+          <t>Profunda</t>
         </is>
       </c>
       <c r="AC19" t="inlineStr">
@@ -2399,7 +2399,7 @@
         <v>0.1</v>
       </c>
       <c r="B20" t="n">
-        <v>0.249538</v>
+        <v>0.248791</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2416,25 +2416,25 @@
         <v>200000</v>
       </c>
       <c r="G20" t="n">
-        <v>0.527007</v>
+        <v>0.532919</v>
       </c>
       <c r="H20" t="n">
-        <v>0.455233</v>
+        <v>0.540984</v>
       </c>
       <c r="I20" t="n">
-        <v>0.488498</v>
+        <v>0.536921</v>
       </c>
       <c r="J20" t="n">
-        <v>0.25062</v>
+        <v>0.251901</v>
       </c>
       <c r="K20" t="n">
-        <v>0.44382</v>
+        <v>0.453659</v>
       </c>
       <c r="L20" t="n">
-        <v>0.42246</v>
+        <v>0.497326</v>
       </c>
       <c r="M20" t="n">
-        <v>0.432877</v>
+        <v>0.47449</v>
       </c>
       <c r="N20" t="n">
         <v>0.2</v>
@@ -2470,7 +2470,7 @@
       </c>
       <c r="X20" t="inlineStr">
         <is>
-          <t>_2_3_3_3_1_1790730015_18.txt</t>
+          <t>_2_3_3_3_1_1790730015_17.txt</t>
         </is>
       </c>
       <c r="Y20" t="inlineStr">
@@ -2500,42 +2500,42 @@
         <v>0.1</v>
       </c>
       <c r="B21" t="n">
-        <v>0.249137</v>
+        <v>0.204325</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>_2_3_3_3_1_</t>
+          <t>_2_9_1_</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>1790730015</v>
+        <v>1790729965</v>
       </c>
       <c r="E21" t="n">
-        <v>127</v>
+        <v>50</v>
       </c>
       <c r="F21" t="n">
         <v>200000</v>
       </c>
       <c r="G21" t="n">
-        <v>0.525358</v>
+        <v>0.675963</v>
       </c>
       <c r="H21" t="n">
-        <v>0.509458</v>
+        <v>0.641866</v>
       </c>
       <c r="I21" t="n">
-        <v>0.517286</v>
+        <v>0.658473</v>
       </c>
       <c r="J21" t="n">
-        <v>0.251934</v>
+        <v>0.21031</v>
       </c>
       <c r="K21" t="n">
-        <v>0.437811</v>
+        <v>0.659091</v>
       </c>
       <c r="L21" t="n">
-        <v>0.470588</v>
+        <v>0.620321</v>
       </c>
       <c r="M21" t="n">
-        <v>0.453608</v>
+        <v>0.639118</v>
       </c>
       <c r="N21" t="n">
         <v>0.2</v>
@@ -2571,23 +2571,23 @@
       </c>
       <c r="X21" t="inlineStr">
         <is>
-          <t>_2_3_3_3_1_1790730015_9.txt</t>
+          <t>_2_9_1_1790729965_0.txt</t>
         </is>
       </c>
       <c r="Y21" t="inlineStr">
         <is>
-          <t>[3, 3, 3]</t>
+          <t>[9]</t>
         </is>
       </c>
       <c r="Z21" t="n">
         <v>9</v>
       </c>
       <c r="AA21" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>Profunda</t>
+          <t>Angosta</t>
         </is>
       </c>
       <c r="AC21" t="inlineStr">
@@ -2601,42 +2601,42 @@
         <v>0.1</v>
       </c>
       <c r="B22" t="n">
-        <v>0.24934</v>
+        <v>0.214497</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>_2_3_3_3_1_</t>
+          <t>_2_9_1_</t>
         </is>
       </c>
       <c r="D22" t="n">
-        <v>1790730015</v>
+        <v>1790729965</v>
       </c>
       <c r="E22" t="n">
-        <v>127</v>
+        <v>50</v>
       </c>
       <c r="F22" t="n">
         <v>200000</v>
       </c>
       <c r="G22" t="n">
-        <v>0.5199009999999999</v>
+        <v>0.635171</v>
       </c>
       <c r="H22" t="n">
-        <v>0.527112</v>
+        <v>0.61034</v>
       </c>
       <c r="I22" t="n">
-        <v>0.523481</v>
+        <v>0.622508</v>
       </c>
       <c r="J22" t="n">
-        <v>0.251775</v>
+        <v>0.215759</v>
       </c>
       <c r="K22" t="n">
-        <v>0.427184</v>
+        <v>0.606557</v>
       </c>
       <c r="L22" t="n">
-        <v>0.470588</v>
+        <v>0.593583</v>
       </c>
       <c r="M22" t="n">
-        <v>0.447837</v>
+        <v>0.6</v>
       </c>
       <c r="N22" t="n">
         <v>0.2</v>
@@ -2672,23 +2672,23 @@
       </c>
       <c r="X22" t="inlineStr">
         <is>
-          <t>_2_3_3_3_1_1790730015_11.txt</t>
+          <t>_2_9_1_1790729965_15.txt</t>
         </is>
       </c>
       <c r="Y22" t="inlineStr">
         <is>
-          <t>[3, 3, 3]</t>
+          <t>[9]</t>
         </is>
       </c>
       <c r="Z22" t="n">
         <v>9</v>
       </c>
       <c r="AA22" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>Profunda</t>
+          <t>Angosta</t>
         </is>
       </c>
       <c r="AC22" t="inlineStr">
@@ -2702,42 +2702,42 @@
         <v>0.1</v>
       </c>
       <c r="B23" t="n">
-        <v>0.213192</v>
+        <v>0.24935</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>_2_9_1_</t>
+          <t>_2_3_3_3_1_</t>
         </is>
       </c>
       <c r="D23" t="n">
-        <v>1790729965</v>
+        <v>1790730015</v>
       </c>
       <c r="E23" t="n">
-        <v>50</v>
+        <v>127</v>
       </c>
       <c r="F23" t="n">
         <v>200000</v>
       </c>
       <c r="G23" t="n">
-        <v>0.643979</v>
+        <v>0.5199009999999999</v>
       </c>
       <c r="H23" t="n">
-        <v>0.620429</v>
+        <v>0.527112</v>
       </c>
       <c r="I23" t="n">
-        <v>0.631985</v>
+        <v>0.523481</v>
       </c>
       <c r="J23" t="n">
-        <v>0.214961</v>
+        <v>0.251762</v>
       </c>
       <c r="K23" t="n">
-        <v>0.598901</v>
+        <v>0.427184</v>
       </c>
       <c r="L23" t="n">
-        <v>0.582888</v>
+        <v>0.470588</v>
       </c>
       <c r="M23" t="n">
-        <v>0.590786</v>
+        <v>0.447837</v>
       </c>
       <c r="N23" t="n">
         <v>0.2</v>
@@ -2773,23 +2773,23 @@
       </c>
       <c r="X23" t="inlineStr">
         <is>
-          <t>_2_9_1_1790729965_18.txt</t>
+          <t>_2_3_3_3_1_1790730015_15.txt</t>
         </is>
       </c>
       <c r="Y23" t="inlineStr">
         <is>
-          <t>[9]</t>
+          <t>[3, 3, 3]</t>
         </is>
       </c>
       <c r="Z23" t="n">
         <v>9</v>
       </c>
       <c r="AA23" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>Angosta</t>
+          <t>Profunda</t>
         </is>
       </c>
       <c r="AC23" t="inlineStr">
@@ -2803,7 +2803,7 @@
         <v>0.1</v>
       </c>
       <c r="B24" t="n">
-        <v>0.249307</v>
+        <v>0.249359</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -2820,25 +2820,25 @@
         <v>200000</v>
       </c>
       <c r="G24" t="n">
-        <v>0.52381</v>
+        <v>0.5199009999999999</v>
       </c>
       <c r="H24" t="n">
         <v>0.527112</v>
       </c>
       <c r="I24" t="n">
-        <v>0.525456</v>
+        <v>0.523481</v>
       </c>
       <c r="J24" t="n">
-        <v>0.251885</v>
+        <v>0.251712</v>
       </c>
       <c r="K24" t="n">
-        <v>0.427184</v>
+        <v>0.425121</v>
       </c>
       <c r="L24" t="n">
         <v>0.470588</v>
       </c>
       <c r="M24" t="n">
-        <v>0.447837</v>
+        <v>0.4467</v>
       </c>
       <c r="N24" t="n">
         <v>0.2</v>
@@ -2874,7 +2874,7 @@
       </c>
       <c r="X24" t="inlineStr">
         <is>
-          <t>_2_3_3_3_1_1790730015_12.txt</t>
+          <t>_2_3_3_3_1_1790730015_5.txt</t>
         </is>
       </c>
       <c r="Y24" t="inlineStr">
@@ -2904,42 +2904,42 @@
         <v>0.1</v>
       </c>
       <c r="B25" t="n">
-        <v>0.249291</v>
+        <v>0.214252</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>_2_3_3_3_1_</t>
+          <t>_2_9_1_</t>
         </is>
       </c>
       <c r="D25" t="n">
-        <v>1790730015</v>
+        <v>1790729965</v>
       </c>
       <c r="E25" t="n">
-        <v>127</v>
+        <v>50</v>
       </c>
       <c r="F25" t="n">
         <v>200000</v>
       </c>
       <c r="G25" t="n">
-        <v>0.5220129999999999</v>
+        <v>0.658537</v>
       </c>
       <c r="H25" t="n">
-        <v>0.523329</v>
+        <v>0.612863</v>
       </c>
       <c r="I25" t="n">
-        <v>0.52267</v>
+        <v>0.634879</v>
       </c>
       <c r="J25" t="n">
-        <v>0.251789</v>
+        <v>0.214906</v>
       </c>
       <c r="K25" t="n">
-        <v>0.426471</v>
+        <v>0.64</v>
       </c>
       <c r="L25" t="n">
-        <v>0.465241</v>
+        <v>0.59893</v>
       </c>
       <c r="M25" t="n">
-        <v>0.445013</v>
+        <v>0.618785</v>
       </c>
       <c r="N25" t="n">
         <v>0.2</v>
@@ -2975,23 +2975,23 @@
       </c>
       <c r="X25" t="inlineStr">
         <is>
-          <t>_2_3_3_3_1_1790730015_1.txt</t>
+          <t>_2_9_1_1790729965_8.txt</t>
         </is>
       </c>
       <c r="Y25" t="inlineStr">
         <is>
-          <t>[3, 3, 3]</t>
+          <t>[9]</t>
         </is>
       </c>
       <c r="Z25" t="n">
         <v>9</v>
       </c>
       <c r="AA25" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>Profunda</t>
+          <t>Angosta</t>
         </is>
       </c>
       <c r="AC25" t="inlineStr">
@@ -3005,42 +3005,42 @@
         <v>0.1</v>
       </c>
       <c r="B26" t="n">
-        <v>0.242723</v>
+        <v>0.249307</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>_2_9_1_</t>
+          <t>_2_3_3_3_1_</t>
         </is>
       </c>
       <c r="D26" t="n">
-        <v>1790729965</v>
+        <v>1790730015</v>
       </c>
       <c r="E26" t="n">
-        <v>50</v>
+        <v>127</v>
       </c>
       <c r="F26" t="n">
         <v>200000</v>
       </c>
       <c r="G26" t="n">
-        <v>0.552404</v>
+        <v>0.52381</v>
       </c>
       <c r="H26" t="n">
-        <v>0.564943</v>
+        <v>0.527112</v>
       </c>
       <c r="I26" t="n">
-        <v>0.558603</v>
+        <v>0.525456</v>
       </c>
       <c r="J26" t="n">
-        <v>0.247625</v>
+        <v>0.251885</v>
       </c>
       <c r="K26" t="n">
-        <v>0.515625</v>
+        <v>0.427184</v>
       </c>
       <c r="L26" t="n">
-        <v>0.529412</v>
+        <v>0.470588</v>
       </c>
       <c r="M26" t="n">
-        <v>0.522427</v>
+        <v>0.447837</v>
       </c>
       <c r="N26" t="n">
         <v>0.2</v>
@@ -3076,23 +3076,23 @@
       </c>
       <c r="X26" t="inlineStr">
         <is>
-          <t>_2_9_1_1790729965_6.txt</t>
+          <t>_2_3_3_3_1_1790730015_12.txt</t>
         </is>
       </c>
       <c r="Y26" t="inlineStr">
         <is>
-          <t>[9]</t>
+          <t>[3, 3, 3]</t>
         </is>
       </c>
       <c r="Z26" t="n">
         <v>9</v>
       </c>
       <c r="AA26" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>Angosta</t>
+          <t>Profunda</t>
         </is>
       </c>
       <c r="AC26" t="inlineStr">
@@ -3106,42 +3106,42 @@
         <v>0.1</v>
       </c>
       <c r="B27" t="n">
-        <v>0.249454</v>
+        <v>0.214526</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>_2_3_3_3_1_</t>
+          <t>_2_9_1_</t>
         </is>
       </c>
       <c r="D27" t="n">
-        <v>1790730015</v>
+        <v>1790729965</v>
       </c>
       <c r="E27" t="n">
-        <v>127</v>
+        <v>50</v>
       </c>
       <c r="F27" t="n">
         <v>200000</v>
       </c>
       <c r="G27" t="n">
-        <v>0.523481</v>
+        <v>0.639893</v>
       </c>
       <c r="H27" t="n">
-        <v>0.477932</v>
+        <v>0.602774</v>
       </c>
       <c r="I27" t="n">
-        <v>0.49967</v>
+        <v>0.620779</v>
       </c>
       <c r="J27" t="n">
-        <v>0.251518</v>
+        <v>0.216178</v>
       </c>
       <c r="K27" t="n">
-        <v>0.444444</v>
+        <v>0.612022</v>
       </c>
       <c r="L27" t="n">
-        <v>0.449198</v>
+        <v>0.59893</v>
       </c>
       <c r="M27" t="n">
-        <v>0.446809</v>
+        <v>0.605405</v>
       </c>
       <c r="N27" t="n">
         <v>0.2</v>
@@ -3177,23 +3177,23 @@
       </c>
       <c r="X27" t="inlineStr">
         <is>
-          <t>_2_3_3_3_1_1790730015_19.txt</t>
+          <t>_2_9_1_1790729965_12.txt</t>
         </is>
       </c>
       <c r="Y27" t="inlineStr">
         <is>
-          <t>[3, 3, 3]</t>
+          <t>[9]</t>
         </is>
       </c>
       <c r="Z27" t="n">
         <v>9</v>
       </c>
       <c r="AA27" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>Profunda</t>
+          <t>Angosta</t>
         </is>
       </c>
       <c r="AC27" t="inlineStr">
@@ -3207,42 +3207,42 @@
         <v>0.1</v>
       </c>
       <c r="B28" t="n">
-        <v>0.249317</v>
+        <v>0.213192</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>_2_3_3_3_1_</t>
+          <t>_2_9_1_</t>
         </is>
       </c>
       <c r="D28" t="n">
-        <v>1790730015</v>
+        <v>1790729965</v>
       </c>
       <c r="E28" t="n">
-        <v>127</v>
+        <v>50</v>
       </c>
       <c r="F28" t="n">
         <v>200000</v>
       </c>
       <c r="G28" t="n">
-        <v>0.526923</v>
+        <v>0.643979</v>
       </c>
       <c r="H28" t="n">
-        <v>0.518285</v>
+        <v>0.620429</v>
       </c>
       <c r="I28" t="n">
-        <v>0.522568</v>
+        <v>0.631985</v>
       </c>
       <c r="J28" t="n">
-        <v>0.251861</v>
+        <v>0.214961</v>
       </c>
       <c r="K28" t="n">
-        <v>0.432161</v>
+        <v>0.598901</v>
       </c>
       <c r="L28" t="n">
-        <v>0.459893</v>
+        <v>0.582888</v>
       </c>
       <c r="M28" t="n">
-        <v>0.445596</v>
+        <v>0.590786</v>
       </c>
       <c r="N28" t="n">
         <v>0.2</v>
@@ -3278,23 +3278,23 @@
       </c>
       <c r="X28" t="inlineStr">
         <is>
-          <t>_2_3_3_3_1_1790730015_2.txt</t>
+          <t>_2_9_1_1790729965_18.txt</t>
         </is>
       </c>
       <c r="Y28" t="inlineStr">
         <is>
-          <t>[3, 3, 3]</t>
+          <t>[9]</t>
         </is>
       </c>
       <c r="Z28" t="n">
         <v>9</v>
       </c>
       <c r="AA28" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>Profunda</t>
+          <t>Angosta</t>
         </is>
       </c>
       <c r="AC28" t="inlineStr">
@@ -3308,42 +3308,42 @@
         <v>0.1</v>
       </c>
       <c r="B29" t="n">
-        <v>0.211687</v>
+        <v>0.249317</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>_2_9_1_</t>
+          <t>_2_3_3_3_1_</t>
         </is>
       </c>
       <c r="D29" t="n">
-        <v>1790729965</v>
+        <v>1790730015</v>
       </c>
       <c r="E29" t="n">
-        <v>50</v>
+        <v>127</v>
       </c>
       <c r="F29" t="n">
         <v>200000</v>
       </c>
       <c r="G29" t="n">
-        <v>0.6815639999999999</v>
+        <v>0.526923</v>
       </c>
       <c r="H29" t="n">
-        <v>0.615385</v>
+        <v>0.518285</v>
       </c>
       <c r="I29" t="n">
-        <v>0.646786</v>
+        <v>0.522568</v>
       </c>
       <c r="J29" t="n">
-        <v>0.210628</v>
+        <v>0.251861</v>
       </c>
       <c r="K29" t="n">
-        <v>0.655367</v>
+        <v>0.432161</v>
       </c>
       <c r="L29" t="n">
-        <v>0.620321</v>
+        <v>0.459893</v>
       </c>
       <c r="M29" t="n">
-        <v>0.637363</v>
+        <v>0.445596</v>
       </c>
       <c r="N29" t="n">
         <v>0.2</v>
@@ -3379,23 +3379,23 @@
       </c>
       <c r="X29" t="inlineStr">
         <is>
-          <t>_2_9_1_1790729965_7.txt</t>
+          <t>_2_3_3_3_1_1790730015_2.txt</t>
         </is>
       </c>
       <c r="Y29" t="inlineStr">
         <is>
-          <t>[9]</t>
+          <t>[3, 3, 3]</t>
         </is>
       </c>
       <c r="Z29" t="n">
         <v>9</v>
       </c>
       <c r="AA29" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>Angosta</t>
+          <t>Profunda</t>
         </is>
       </c>
       <c r="AC29" t="inlineStr">
@@ -3409,42 +3409,42 @@
         <v>0.1</v>
       </c>
       <c r="B30" t="n">
-        <v>0.214526</v>
+        <v>0.24929</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>_2_9_1_</t>
+          <t>_2_3_3_3_1_</t>
         </is>
       </c>
       <c r="D30" t="n">
-        <v>1790729965</v>
+        <v>1790730015</v>
       </c>
       <c r="E30" t="n">
-        <v>50</v>
+        <v>127</v>
       </c>
       <c r="F30" t="n">
         <v>200000</v>
       </c>
       <c r="G30" t="n">
-        <v>0.639893</v>
+        <v>0.521848</v>
       </c>
       <c r="H30" t="n">
-        <v>0.602774</v>
+        <v>0.527112</v>
       </c>
       <c r="I30" t="n">
-        <v>0.620779</v>
+        <v>0.524467</v>
       </c>
       <c r="J30" t="n">
-        <v>0.216178</v>
+        <v>0.251764</v>
       </c>
       <c r="K30" t="n">
-        <v>0.612022</v>
+        <v>0.427184</v>
       </c>
       <c r="L30" t="n">
-        <v>0.59893</v>
+        <v>0.470588</v>
       </c>
       <c r="M30" t="n">
-        <v>0.605405</v>
+        <v>0.447837</v>
       </c>
       <c r="N30" t="n">
         <v>0.2</v>
@@ -3480,23 +3480,23 @@
       </c>
       <c r="X30" t="inlineStr">
         <is>
-          <t>_2_9_1_1790729965_12.txt</t>
+          <t>_2_3_3_3_1_1790730015_6.txt</t>
         </is>
       </c>
       <c r="Y30" t="inlineStr">
         <is>
-          <t>[9]</t>
+          <t>[3, 3, 3]</t>
         </is>
       </c>
       <c r="Z30" t="n">
         <v>9</v>
       </c>
       <c r="AA30" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>Angosta</t>
+          <t>Profunda</t>
         </is>
       </c>
       <c r="AC30" t="inlineStr">
@@ -3510,42 +3510,42 @@
         <v>0.1</v>
       </c>
       <c r="B31" t="n">
-        <v>0.249301</v>
+        <v>0.220848</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>_2_3_3_3_1_</t>
+          <t>_2_9_1_</t>
         </is>
       </c>
       <c r="D31" t="n">
-        <v>1790730015</v>
+        <v>1790729965</v>
       </c>
       <c r="E31" t="n">
-        <v>127</v>
+        <v>50</v>
       </c>
       <c r="F31" t="n">
         <v>200000</v>
       </c>
       <c r="G31" t="n">
-        <v>0.514151</v>
+        <v>0.582147</v>
       </c>
       <c r="H31" t="n">
-        <v>0.549811</v>
+        <v>0.567465</v>
       </c>
       <c r="I31" t="n">
-        <v>0.531383</v>
+        <v>0.574713</v>
       </c>
       <c r="J31" t="n">
-        <v>0.251577</v>
+        <v>0.220998</v>
       </c>
       <c r="K31" t="n">
-        <v>0.438356</v>
+        <v>0.576271</v>
       </c>
       <c r="L31" t="n">
-        <v>0.513369</v>
+        <v>0.545455</v>
       </c>
       <c r="M31" t="n">
-        <v>0.472906</v>
+        <v>0.56044</v>
       </c>
       <c r="N31" t="n">
         <v>0.2</v>
@@ -3581,23 +3581,23 @@
       </c>
       <c r="X31" t="inlineStr">
         <is>
-          <t>_2_3_3_3_1_1790730015_10.txt</t>
+          <t>_2_9_1_1790729965_16.txt</t>
         </is>
       </c>
       <c r="Y31" t="inlineStr">
         <is>
-          <t>[3, 3, 3]</t>
+          <t>[9]</t>
         </is>
       </c>
       <c r="Z31" t="n">
         <v>9</v>
       </c>
       <c r="AA31" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>Profunda</t>
+          <t>Angosta</t>
         </is>
       </c>
       <c r="AC31" t="inlineStr">
@@ -3611,42 +3611,42 @@
         <v>0.1</v>
       </c>
       <c r="B32" t="n">
-        <v>0.224132</v>
+        <v>0.249263</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>_2_9_1_</t>
+          <t>_2_3_3_3_1_</t>
         </is>
       </c>
       <c r="D32" t="n">
-        <v>1790729965</v>
+        <v>1790730015</v>
       </c>
       <c r="E32" t="n">
-        <v>50</v>
+        <v>127</v>
       </c>
       <c r="F32" t="n">
         <v>200000</v>
       </c>
       <c r="G32" t="n">
-        <v>0.581019</v>
+        <v>0.526786</v>
       </c>
       <c r="H32" t="n">
-        <v>0.633039</v>
+        <v>0.520807</v>
       </c>
       <c r="I32" t="n">
-        <v>0.605914</v>
+        <v>0.523779</v>
       </c>
       <c r="J32" t="n">
-        <v>0.226038</v>
+        <v>0.251961</v>
       </c>
       <c r="K32" t="n">
-        <v>0.539906</v>
+        <v>0.43</v>
       </c>
       <c r="L32" t="n">
-        <v>0.614973</v>
+        <v>0.459893</v>
       </c>
       <c r="M32" t="n">
-        <v>0.575</v>
+        <v>0.444444</v>
       </c>
       <c r="N32" t="n">
         <v>0.2</v>
@@ -3682,23 +3682,23 @@
       </c>
       <c r="X32" t="inlineStr">
         <is>
-          <t>_2_9_1_1790729965_13.txt</t>
+          <t>_2_3_3_3_1_1790730015_0.txt</t>
         </is>
       </c>
       <c r="Y32" t="inlineStr">
         <is>
-          <t>[9]</t>
+          <t>[3, 3, 3]</t>
         </is>
       </c>
       <c r="Z32" t="n">
         <v>9</v>
       </c>
       <c r="AA32" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>Angosta</t>
+          <t>Profunda</t>
         </is>
       </c>
       <c r="AC32" t="inlineStr">
@@ -3712,42 +3712,42 @@
         <v>0.1</v>
       </c>
       <c r="B33" t="n">
-        <v>0.24929</v>
+        <v>0.224132</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>_2_3_3_3_1_</t>
+          <t>_2_9_1_</t>
         </is>
       </c>
       <c r="D33" t="n">
-        <v>1790730015</v>
+        <v>1790729965</v>
       </c>
       <c r="E33" t="n">
-        <v>127</v>
+        <v>50</v>
       </c>
       <c r="F33" t="n">
         <v>200000</v>
       </c>
       <c r="G33" t="n">
-        <v>0.521848</v>
+        <v>0.581019</v>
       </c>
       <c r="H33" t="n">
-        <v>0.527112</v>
+        <v>0.633039</v>
       </c>
       <c r="I33" t="n">
-        <v>0.524467</v>
+        <v>0.605914</v>
       </c>
       <c r="J33" t="n">
-        <v>0.251764</v>
+        <v>0.226038</v>
       </c>
       <c r="K33" t="n">
-        <v>0.427184</v>
+        <v>0.539906</v>
       </c>
       <c r="L33" t="n">
-        <v>0.470588</v>
+        <v>0.614973</v>
       </c>
       <c r="M33" t="n">
-        <v>0.447837</v>
+        <v>0.575</v>
       </c>
       <c r="N33" t="n">
         <v>0.2</v>
@@ -3783,23 +3783,23 @@
       </c>
       <c r="X33" t="inlineStr">
         <is>
-          <t>_2_3_3_3_1_1790730015_6.txt</t>
+          <t>_2_9_1_1790729965_13.txt</t>
         </is>
       </c>
       <c r="Y33" t="inlineStr">
         <is>
-          <t>[3, 3, 3]</t>
+          <t>[9]</t>
         </is>
       </c>
       <c r="Z33" t="n">
         <v>9</v>
       </c>
       <c r="AA33" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>Profunda</t>
+          <t>Angosta</t>
         </is>
       </c>
       <c r="AC33" t="inlineStr">
@@ -3813,7 +3813,7 @@
         <v>0.1</v>
       </c>
       <c r="B34" t="n">
-        <v>0.241282</v>
+        <v>0.194465</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -3830,25 +3830,25 @@
         <v>200000</v>
       </c>
       <c r="G34" t="n">
-        <v>0.577778</v>
+        <v>0.730159</v>
       </c>
       <c r="H34" t="n">
-        <v>0.491803</v>
+        <v>0.580076</v>
       </c>
       <c r="I34" t="n">
-        <v>0.531335</v>
+        <v>0.646521</v>
       </c>
       <c r="J34" t="n">
-        <v>0.241958</v>
+        <v>0.207262</v>
       </c>
       <c r="K34" t="n">
-        <v>0.55625</v>
+        <v>0.682759</v>
       </c>
       <c r="L34" t="n">
-        <v>0.475936</v>
+        <v>0.529412</v>
       </c>
       <c r="M34" t="n">
-        <v>0.512968</v>
+        <v>0.596386</v>
       </c>
       <c r="N34" t="n">
         <v>0.2</v>
@@ -3884,7 +3884,7 @@
       </c>
       <c r="X34" t="inlineStr">
         <is>
-          <t>_2_9_1_1790729965_14.txt</t>
+          <t>_2_9_1_1790729965_17.txt</t>
         </is>
       </c>
       <c r="Y34" t="inlineStr">
@@ -3914,7 +3914,7 @@
         <v>0.1</v>
       </c>
       <c r="B35" t="n">
-        <v>0.212708</v>
+        <v>0.222569</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -3931,25 +3931,25 @@
         <v>200000</v>
       </c>
       <c r="G35" t="n">
-        <v>0.647712</v>
+        <v>0.63135</v>
       </c>
       <c r="H35" t="n">
-        <v>0.588903</v>
+        <v>0.54855</v>
       </c>
       <c r="I35" t="n">
-        <v>0.616909</v>
+        <v>0.587045</v>
       </c>
       <c r="J35" t="n">
-        <v>0.215801</v>
+        <v>0.225336</v>
       </c>
       <c r="K35" t="n">
-        <v>0.61875</v>
+        <v>0.6</v>
       </c>
       <c r="L35" t="n">
-        <v>0.529412</v>
+        <v>0.5775400000000001</v>
       </c>
       <c r="M35" t="n">
-        <v>0.570605</v>
+        <v>0.588556</v>
       </c>
       <c r="N35" t="n">
         <v>0.2</v>
@@ -3985,7 +3985,7 @@
       </c>
       <c r="X35" t="inlineStr">
         <is>
-          <t>_2_9_1_1790729965_9.txt</t>
+          <t>_2_9_1_1790729965_10.txt</t>
         </is>
       </c>
       <c r="Y35" t="inlineStr">
@@ -4015,42 +4015,42 @@
         <v>0.1</v>
       </c>
       <c r="B36" t="n">
-        <v>0.249165</v>
+        <v>0.215543</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>_2_3_3_3_1_</t>
+          <t>_2_9_1_</t>
         </is>
       </c>
       <c r="D36" t="n">
-        <v>1790730015</v>
+        <v>1790729965</v>
       </c>
       <c r="E36" t="n">
-        <v>127</v>
+        <v>50</v>
       </c>
       <c r="F36" t="n">
         <v>200000</v>
       </c>
       <c r="G36" t="n">
-        <v>0.524528</v>
+        <v>0.673177</v>
       </c>
       <c r="H36" t="n">
-        <v>0.525851</v>
+        <v>0.651955</v>
       </c>
       <c r="I36" t="n">
-        <v>0.525189</v>
+        <v>0.662396</v>
       </c>
       <c r="J36" t="n">
-        <v>0.251801</v>
+        <v>0.228765</v>
       </c>
       <c r="K36" t="n">
-        <v>0.42233</v>
+        <v>0.601064</v>
       </c>
       <c r="L36" t="n">
-        <v>0.465241</v>
+        <v>0.604278</v>
       </c>
       <c r="M36" t="n">
-        <v>0.442748</v>
+        <v>0.602667</v>
       </c>
       <c r="N36" t="n">
         <v>0.2</v>
@@ -4086,23 +4086,23 @@
       </c>
       <c r="X36" t="inlineStr">
         <is>
-          <t>_2_3_3_3_1_1790730015_3.txt</t>
+          <t>_2_9_1_1790729965_4.txt</t>
         </is>
       </c>
       <c r="Y36" t="inlineStr">
         <is>
-          <t>[3, 3, 3]</t>
+          <t>[9]</t>
         </is>
       </c>
       <c r="Z36" t="n">
         <v>9</v>
       </c>
       <c r="AA36" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>Profunda</t>
+          <t>Angosta</t>
         </is>
       </c>
       <c r="AC36" t="inlineStr">
@@ -4116,42 +4116,42 @@
         <v>0.1</v>
       </c>
       <c r="B37" t="n">
-        <v>0.248857</v>
+        <v>0.242723</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>_2_3_3_3_1_</t>
+          <t>_2_9_1_</t>
         </is>
       </c>
       <c r="D37" t="n">
-        <v>1790730015</v>
+        <v>1790729965</v>
       </c>
       <c r="E37" t="n">
-        <v>127</v>
+        <v>50</v>
       </c>
       <c r="F37" t="n">
         <v>200000</v>
       </c>
       <c r="G37" t="n">
-        <v>0.508259</v>
+        <v>0.552404</v>
       </c>
       <c r="H37" t="n">
-        <v>0.504414</v>
+        <v>0.564943</v>
       </c>
       <c r="I37" t="n">
-        <v>0.506329</v>
+        <v>0.558603</v>
       </c>
       <c r="J37" t="n">
-        <v>0.252</v>
+        <v>0.247625</v>
       </c>
       <c r="K37" t="n">
-        <v>0.419512</v>
+        <v>0.515625</v>
       </c>
       <c r="L37" t="n">
-        <v>0.459893</v>
+        <v>0.529412</v>
       </c>
       <c r="M37" t="n">
-        <v>0.438776</v>
+        <v>0.522427</v>
       </c>
       <c r="N37" t="n">
         <v>0.2</v>
@@ -4187,23 +4187,23 @@
       </c>
       <c r="X37" t="inlineStr">
         <is>
-          <t>_2_3_3_3_1_1790730015_8.txt</t>
+          <t>_2_9_1_1790729965_6.txt</t>
         </is>
       </c>
       <c r="Y37" t="inlineStr">
         <is>
-          <t>[3, 3, 3]</t>
+          <t>[9]</t>
         </is>
       </c>
       <c r="Z37" t="n">
         <v>9</v>
       </c>
       <c r="AA37" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>Profunda</t>
+          <t>Angosta</t>
         </is>
       </c>
       <c r="AC37" t="inlineStr">
@@ -4217,42 +4217,42 @@
         <v>0.1</v>
       </c>
       <c r="B38" t="n">
-        <v>0.249263</v>
+        <v>0.212708</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>_2_3_3_3_1_</t>
+          <t>_2_9_1_</t>
         </is>
       </c>
       <c r="D38" t="n">
-        <v>1790730015</v>
+        <v>1790729965</v>
       </c>
       <c r="E38" t="n">
-        <v>127</v>
+        <v>50</v>
       </c>
       <c r="F38" t="n">
         <v>200000</v>
       </c>
       <c r="G38" t="n">
-        <v>0.526786</v>
+        <v>0.647712</v>
       </c>
       <c r="H38" t="n">
-        <v>0.520807</v>
+        <v>0.588903</v>
       </c>
       <c r="I38" t="n">
-        <v>0.523779</v>
+        <v>0.616909</v>
       </c>
       <c r="J38" t="n">
-        <v>0.251961</v>
+        <v>0.215801</v>
       </c>
       <c r="K38" t="n">
-        <v>0.43</v>
+        <v>0.61875</v>
       </c>
       <c r="L38" t="n">
-        <v>0.459893</v>
+        <v>0.529412</v>
       </c>
       <c r="M38" t="n">
-        <v>0.444444</v>
+        <v>0.570605</v>
       </c>
       <c r="N38" t="n">
         <v>0.2</v>
@@ -4288,23 +4288,23 @@
       </c>
       <c r="X38" t="inlineStr">
         <is>
-          <t>_2_3_3_3_1_1790730015_0.txt</t>
+          <t>_2_9_1_1790729965_9.txt</t>
         </is>
       </c>
       <c r="Y38" t="inlineStr">
         <is>
-          <t>[3, 3, 3]</t>
+          <t>[9]</t>
         </is>
       </c>
       <c r="Z38" t="n">
         <v>9</v>
       </c>
       <c r="AA38" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>Profunda</t>
+          <t>Angosta</t>
         </is>
       </c>
       <c r="AC38" t="inlineStr">
@@ -4318,42 +4318,42 @@
         <v>0.1</v>
       </c>
       <c r="B39" t="n">
-        <v>0.204325</v>
+        <v>0.249301</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>_2_9_1_</t>
+          <t>_2_3_3_3_1_</t>
         </is>
       </c>
       <c r="D39" t="n">
-        <v>1790729965</v>
+        <v>1790730015</v>
       </c>
       <c r="E39" t="n">
-        <v>50</v>
+        <v>127</v>
       </c>
       <c r="F39" t="n">
         <v>200000</v>
       </c>
       <c r="G39" t="n">
-        <v>0.675963</v>
+        <v>0.514151</v>
       </c>
       <c r="H39" t="n">
-        <v>0.641866</v>
+        <v>0.549811</v>
       </c>
       <c r="I39" t="n">
-        <v>0.658473</v>
+        <v>0.531383</v>
       </c>
       <c r="J39" t="n">
-        <v>0.21031</v>
+        <v>0.251577</v>
       </c>
       <c r="K39" t="n">
-        <v>0.659091</v>
+        <v>0.438356</v>
       </c>
       <c r="L39" t="n">
-        <v>0.620321</v>
+        <v>0.513369</v>
       </c>
       <c r="M39" t="n">
-        <v>0.639118</v>
+        <v>0.472906</v>
       </c>
       <c r="N39" t="n">
         <v>0.2</v>
@@ -4389,23 +4389,23 @@
       </c>
       <c r="X39" t="inlineStr">
         <is>
-          <t>_2_9_1_1790729965_0.txt</t>
+          <t>_2_3_3_3_1_1790730015_10.txt</t>
         </is>
       </c>
       <c r="Y39" t="inlineStr">
         <is>
-          <t>[9]</t>
+          <t>[3, 3, 3]</t>
         </is>
       </c>
       <c r="Z39" t="n">
         <v>9</v>
       </c>
       <c r="AA39" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>Angosta</t>
+          <t>Profunda</t>
         </is>
       </c>
       <c r="AC39" t="inlineStr">
@@ -4419,7 +4419,7 @@
         <v>0.1</v>
       </c>
       <c r="B40" t="n">
-        <v>0.222569</v>
+        <v>0.215814</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -4436,25 +4436,25 @@
         <v>200000</v>
       </c>
       <c r="G40" t="n">
-        <v>0.63135</v>
+        <v>0.635838</v>
       </c>
       <c r="H40" t="n">
-        <v>0.54855</v>
+        <v>0.554855</v>
       </c>
       <c r="I40" t="n">
-        <v>0.587045</v>
+        <v>0.592593</v>
       </c>
       <c r="J40" t="n">
-        <v>0.225336</v>
+        <v>0.216246</v>
       </c>
       <c r="K40" t="n">
-        <v>0.6</v>
+        <v>0.63354</v>
       </c>
       <c r="L40" t="n">
-        <v>0.5775400000000001</v>
+        <v>0.545455</v>
       </c>
       <c r="M40" t="n">
-        <v>0.588556</v>
+        <v>0.586207</v>
       </c>
       <c r="N40" t="n">
         <v>0.2</v>
@@ -4490,7 +4490,7 @@
       </c>
       <c r="X40" t="inlineStr">
         <is>
-          <t>_2_9_1_1790729965_10.txt</t>
+          <t>_2_9_1_1790729965_1.txt</t>
         </is>
       </c>
       <c r="Y40" t="inlineStr">
@@ -4520,42 +4520,42 @@
         <v>0.1</v>
       </c>
       <c r="B41" t="n">
-        <v>0.248791</v>
+        <v>0.214417</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>_2_3_3_3_1_</t>
+          <t>_2_9_1_</t>
         </is>
       </c>
       <c r="D41" t="n">
-        <v>1790730015</v>
+        <v>1790729965</v>
       </c>
       <c r="E41" t="n">
-        <v>127</v>
+        <v>50</v>
       </c>
       <c r="F41" t="n">
         <v>200000</v>
       </c>
       <c r="G41" t="n">
-        <v>0.532919</v>
+        <v>0.654619</v>
       </c>
       <c r="H41" t="n">
-        <v>0.540984</v>
+        <v>0.616646</v>
       </c>
       <c r="I41" t="n">
-        <v>0.536921</v>
+        <v>0.635065</v>
       </c>
       <c r="J41" t="n">
-        <v>0.251901</v>
+        <v>0.216019</v>
       </c>
       <c r="K41" t="n">
-        <v>0.453659</v>
+        <v>0.6277779999999999</v>
       </c>
       <c r="L41" t="n">
-        <v>0.497326</v>
+        <v>0.604278</v>
       </c>
       <c r="M41" t="n">
-        <v>0.47449</v>
+        <v>0.615804</v>
       </c>
       <c r="N41" t="n">
         <v>0.2</v>
@@ -4591,23 +4591,23 @@
       </c>
       <c r="X41" t="inlineStr">
         <is>
-          <t>_2_3_3_3_1_1790730015_17.txt</t>
+          <t>_2_9_1_1790729965_2.txt</t>
         </is>
       </c>
       <c r="Y41" t="inlineStr">
         <is>
-          <t>[3, 3, 3]</t>
+          <t>[9]</t>
         </is>
       </c>
       <c r="Z41" t="n">
         <v>9</v>
       </c>
       <c r="AA41" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>Profunda</t>
+          <t>Angosta</t>
         </is>
       </c>
       <c r="AC41" t="inlineStr">
@@ -4682,7 +4682,7 @@
         <v>0.44926605</v>
       </c>
       <c r="C2" t="n">
-        <v>0.01009474350173344</v>
+        <v>0.01009474350173343</v>
       </c>
       <c r="D2" t="n">
         <v>0.47449</v>
@@ -4710,7 +4710,7 @@
         <v>0.5882875000000001</v>
       </c>
       <c r="C3" t="n">
-        <v>0.03359298777470648</v>
+        <v>0.03359298777470646</v>
       </c>
       <c r="D3" t="n">
         <v>0.639118</v>
